--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2278</v>
+        <v>3059</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1814</v>
+        <v>2390</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1390</v>
+        <v>1953</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>216</v>
+        <v>309</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>299</v>
+        <v>405</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>256</v>
+        <v>348</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>153</v>
+        <v>212</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>464</v>
+        <v>620</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,47 +875,47 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>205</v>
+        <v>268</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>183</v>
+        <v>258</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>179</v>
+        <v>233</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>254</v>
+        <v>320</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>02591</t>
+          <t>01805</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>VOGHERA</t>
+          <t>APPIANO GENTILE</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,35 +925,35 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>212</v>
+        <v>348</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>128</v>
+        <v>186</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>135</v>
+        <v>303</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>01805</t>
+          <t>02591</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>APPIANO GENTILE</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>28</v>
+        <v>116</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,47 +1037,47 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,51 +1087,51 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>129</v>
+        <v>284</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>52</v>
+        <v>116</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>116</v>
+        <v>241</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1307,35 +1307,35 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>02566</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>PAVIA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>171</v>
+        <v>279</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>98</v>
+        <v>243</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02566</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PAVIA</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,31 +1577,31 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,47 +1631,47 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G28" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>89</v>
-      </c>
       <c r="H28" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J28" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K28" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K28" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L28" s="12" t="n">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,35 +1793,35 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1847,31 +1847,31 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1901,47 +1901,47 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F31" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="M31" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G31" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>91</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1955,47 +1955,47 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F34" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I34" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="J34" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2117,31 +2117,31 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H35" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L35" s="12" t="n">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J37" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2333,47 +2333,47 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,39 +2383,39 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2441,31 +2441,31 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I41" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01923</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CANTÙ</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,39 +2491,39 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J42" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K42" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K42" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2549,28 +2549,28 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>2</v>
@@ -2584,12 +2584,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>01923</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>CANTÙ</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,32 +2599,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>620</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.07903225806451612</v>
+        <v>49</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>320</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.778125</v>
+        <v>249</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>303</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.1188118811881188</v>
+        <v>36</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>178</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.651685393258427</v>
+        <v>116</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>184</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.3043478260869565</v>
+        <v>56</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>173</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.3005780346820809</v>
+        <v>52</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>284</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.0352112676056338</v>
+        <v>10</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>241</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.04149377593360996</v>
+        <v>10</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>215</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.05116279069767442</v>
+        <v>11</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>145</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.2689655172413793</v>
+        <v>39</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>176</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.2102272727272727</v>
+        <v>37</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>279</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.1612903225806452</v>
+        <v>45</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>243</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.2716049382716049</v>
+        <v>66</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>129</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.09302325581395349</v>
+        <v>12</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>176</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.3181818181818182</v>
+        <v>56</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>124</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.8629032258064516</v>
+        <v>107</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>145</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.1310344827586207</v>
+        <v>19</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>63</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.03174603174603174</v>
+        <v>2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>123</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.1219512195121951</v>
+        <v>15</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>96</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.34375</v>
+        <v>33</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>112</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.1696428571428572</v>
+        <v>19</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>110</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.5363636363636364</v>
+        <v>59</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>98</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0.07142857142857142</v>
+        <v>7</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>101</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.0297029702970297</v>
+        <v>3</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>41</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.0975609756097561</v>
+        <v>4</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>98</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.06122448979591837</v>
+        <v>6</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>55</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0.07272727272727272</v>
+        <v>4</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>75</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0.01333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0.06666666666666667</v>
+        <v>3</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>60</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0.2666666666666667</v>
+        <v>16</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>58</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0.05172413793103448</v>
+        <v>3</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>8</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>25</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>0.08</v>
+        <v>2</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3059</v>
+        <v>3253</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2390</v>
+        <v>2531</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1953</v>
+        <v>2102</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="H11" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>620</v>
+        <v>663</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,47 +875,47 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>01805</t>
+          <t>02591</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>APPIANO GENTILE</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,35 +925,35 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>348</v>
+        <v>296</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>303</v>
+        <v>196</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02591</t>
+          <t>01805</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>VOGHERA</t>
+          <t>APPIANO GENTILE</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>279</v>
+        <v>377</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>178</v>
+        <v>327</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>143</v>
+        <v>222</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,39 +1087,39 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>14</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,47 +1199,47 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01919</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>215</v>
+        <v>153</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>01919</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,39 +1303,39 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>150</v>
+        <v>197</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>14</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>24</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1415,35 +1415,35 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1469,19 +1469,19 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>31</v>
@@ -1490,10 +1490,10 @@
         <v>30</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,35 +1631,35 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1688,25 +1688,25 @@
         <v>62</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>91</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>53</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>19</v>
@@ -1742,7 +1742,7 @@
         <v>60</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>48</v>
@@ -1760,7 +1760,7 @@
         <v>15</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>2</v>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>15</v>
@@ -1805,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>7</v>
@@ -1814,14 +1814,14 @@
         <v>20</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>15</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J30" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K30" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K30" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="L30" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>33</v>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>94</v>
+        <v>47</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,39 +1951,39 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>2</v>
@@ -2021,19 +2021,19 @@
         <v>4</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J33" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>98</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2063,16 +2063,16 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>26</v>
@@ -2081,13 +2081,13 @@
         <v>5</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>51</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="H36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J36" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="K36" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02597</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SANNAZZARO DE' BURGONDI</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,32 +2221,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>4</v>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>02597</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>SANNAZZARO DE' BURGONDI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,35 +2275,35 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
         <v>30</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2333,19 +2333,19 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>41</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>6</v>
@@ -2354,10 +2354,10 @@
         <v>1</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2387,19 +2387,19 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>19</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>18</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>5</v>
@@ -2408,14 +2408,14 @@
         <v>3</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2441,16 +2441,16 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>11</v>
@@ -2459,10 +2459,10 @@
         <v>1</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>3</v>
@@ -2495,28 +2495,28 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>1</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>38</v>
@@ -2561,16 +2561,16 @@
         <v>5</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>2</v>
@@ -2606,13 +2606,13 @@
         <v>7</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>5</v>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -525,7 +525,7 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2592,11 +2592,7 @@
           <t>CANTÙ</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>RAVA CLAUDIO</t>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -2642,11 +2642,7 @@
           <t>VALMADRERA</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
           <t>ADINOLFI VINCENZO</t>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3253</v>
+        <v>3445</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2531</v>
+        <v>2668</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2102</v>
+        <v>2250</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>01827</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>ERBA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,51 +1033,51 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>222</v>
+        <v>162</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01827</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ERBA</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,51 +1087,51 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>193</v>
+        <v>320</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>308</v>
+        <v>199</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>11</v>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>42</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>45</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1415,35 +1415,35 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1469,31 +1469,31 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>30</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,31 +1523,31 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>13</v>
+        <v>116</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,39 +1627,39 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>91</v>
@@ -1697,19 +1697,19 @@
         <v>5</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1754,32 +1754,32 @@
         <v>47</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1793,47 +1793,47 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="G29" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="12" t="n">
+      <c r="K29" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J29" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>128</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1847,35 +1847,35 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F30" s="12" t="n">
-        <v>86</v>
-      </c>
       <c r="G30" s="12" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>37</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1955,16 +1955,16 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>95</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>32</v>
@@ -1973,17 +1973,17 @@
         <v>13</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2009,31 +2009,31 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2117,31 +2117,31 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K35" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="M35" s="12" t="n">
         <v>5</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J36" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>121</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>7</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2228,13 +2228,13 @@
         <v>31</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>26</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>22</v>
@@ -2282,7 +2282,7 @@
         <v>30</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>17</v>
@@ -2300,26 +2300,26 @@
         <v>6</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>22</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K39" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2387,31 +2387,31 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="H40" s="12" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2441,28 +2441,28 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>3</v>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>7</v>
@@ -2561,10 +2561,10 @@
         <v>5</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>0</v>
@@ -2602,13 +2602,13 @@
         <v>7</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>5</v>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3445</v>
+        <v>3646</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2668</v>
+        <v>2828</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2250</v>
+        <v>2376</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>700</v>
+        <v>733</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="F12" s="12" t="n">
+        <v>299</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>215</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>277</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>149</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>371</v>
+      </c>
+      <c r="M12" s="12" t="n">
         <v>282</v>
       </c>
-      <c r="G12" s="12" t="n">
-        <v>199</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>263</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>146</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>356</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>275</v>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>55</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="F15" s="12" t="n">
         <v>173</v>
       </c>
-      <c r="F15" s="12" t="n">
-        <v>162</v>
-      </c>
       <c r="G15" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>MELEGNANO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="H16" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="J16" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>42</v>
-      </c>
       <c r="K16" s="12" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>320</v>
+        <v>213</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>51958</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MELEGNANO</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>199</v>
+        <v>335</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,39 +1195,39 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>146</v>
+        <v>248</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="H18" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="K18" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>108</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>60</v>
-      </c>
       <c r="L18" s="12" t="n">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01919</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>01919</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1415,47 +1415,47 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>269</v>
+        <v>204</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,39 +1519,39 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>197</v>
+        <v>282</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1577,35 +1577,35 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G26" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I26" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="H26" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>66</v>
-      </c>
       <c r="J26" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>37</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1688,13 +1688,13 @@
         <v>66</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>91</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>55</v>
@@ -1706,7 +1706,7 @@
         <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>20</v>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,39 +1789,39 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="G29" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I29" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J29" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K29" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K29" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L29" s="12" t="n">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>17</v>
@@ -1859,23 +1859,23 @@
         <v>1</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,39 +1951,39 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>95</v>
+        <v>19</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>3</v>
@@ -2021,19 +2021,19 @@
         <v>4</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2171,31 +2171,31 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K36" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>121</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,12 +2206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2279,31 +2279,31 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H38" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L38" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,51 +2329,51 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>22</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,35 +2383,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H40" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L40" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="12" t="n">
-        <v>49</v>
-      </c>
       <c r="M40" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,35 +2437,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
         <v>23</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
         <v>3</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>14</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>7</v>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>2</v>
@@ -2602,13 +2602,13 @@
         <v>7</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>5</v>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3646</v>
+        <v>3874</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2828</v>
+        <v>2999</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2376</v>
+        <v>2560</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>488</v>
+        <v>523</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>733</v>
+        <v>775</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>54</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H16" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="K16" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>146</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="L16" s="12" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,51 +1141,51 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>250</v>
+        <v>163</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>221</v>
+        <v>351</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,104 +1234,104 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>190</v>
+        <v>263</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>283</v>
+        <v>183</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>12</v>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>204</v>
+        <v>295</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>282</v>
+        <v>219</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,51 +1573,51 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,39 +1627,39 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>26</v>
+        <v>134</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>91</v>
@@ -1697,7 +1697,7 @@
         <v>6</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>23</v>
@@ -1706,7 +1706,7 @@
         <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>20</v>
@@ -1739,31 +1739,31 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,31 +1793,31 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>24</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,20 +1843,20 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>38</v>
@@ -1865,13 +1865,13 @@
         <v>9</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,51 +1897,51 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J32" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K32" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K32" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L32" s="12" t="n">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,39 +2005,39 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H33" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L33" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2063,28 +2063,28 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F34" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="I34" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>110</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="J34" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>21</v>
@@ -2117,28 +2117,28 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>51</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>1</v>
@@ -2171,16 +2171,16 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>30</v>
@@ -2189,17 +2189,17 @@
         <v>7</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2228,32 +2228,32 @@
         <v>37</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>8</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2279,19 +2279,19 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>6</v>
@@ -2300,7 +2300,7 @@
         <v>7</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>7</v>
@@ -2336,13 +2336,13 @@
         <v>31</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>26</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>22</v>
@@ -2387,19 +2387,19 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>2</v>
@@ -2408,7 +2408,7 @@
         <v>12</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>3</v>
@@ -2444,13 +2444,13 @@
         <v>23</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>20</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>23</v>
@@ -2462,10 +2462,10 @@
         <v>1</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>5</v>
@@ -2516,10 +2516,10 @@
         <v>3</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>42</v>
@@ -2561,16 +2561,16 @@
         <v>5</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>2</v>
@@ -2602,13 +2602,13 @@
         <v>7</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>5</v>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -2592,7 +2592,11 @@
           <t>CANTÙ</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>RAVA CLAUDIO</t>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -2592,11 +2592,7 @@
           <t>CANTÙ</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>RAVA CLAUDIO</t>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -525,7 +525,7 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Nadir Abdel</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N45" headerRowCount="1">
-  <autoFilter ref="A10:N45"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O45" headerRowCount="1">
+  <autoFilter ref="A10:O45"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MATTEOTTI 133</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>386</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>523</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>427</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>261</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>775</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>V. MATTEOTTI ANG. COMO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>334</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>318</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>229</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>156</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>385</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>295</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA CARLO EMANUELE 5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>276</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>351</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>127</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>221</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>STRADA PROV.LE N.23</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>273</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>443</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>396</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MILANO 10</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>196</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>228</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA EMILIA, 70</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>255</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>227</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE EUROPA/LIGURIA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>295</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>269</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>351</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>V.LE BRIANZA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>232</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>209</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA ROSSELLI 19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>161</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>231</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>129</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>268</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VAI CAMILLO CAMPARI</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>255</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>338</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VL EUROPA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>85</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>35</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L23" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>295</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>129</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>219</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 36 KM 30+083</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>77</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>39</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>39</v>
       </c>
       <c r="L25" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M25" s="12" t="n">
         <v>172</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE DEI MILLE</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA CECILIO 1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>TRIESTE ANG.GARIBALDI</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE PAPINIANO  54 54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS.234 KM 9+250</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA DI VITTORIO, 14</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SS 10 KM 154+108</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA GALLARATE 40</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA GARIBALDI 197</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MURAT 14</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>PL LOTTO 14/A ANG VI ELIA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>142</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA F.LLI ROSSELLI, N. 17</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>DELLERBA ALBERTO</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2324,42 +2480,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA CERCA  FRAZ.CALEPPIO 21</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="I39" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="J39" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="K39" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="12" t="n">
+      <c r="L39" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L39" s="12" t="n">
+      <c r="M39" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="N39" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2378,42 +2539,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>SP 35 DEI GIOVI KM 132+300</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="I40" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="J40" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K40" s="12" t="n">
+      <c r="L40" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L40" s="12" t="n">
+      <c r="M40" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M40" s="12" t="n">
+      <c r="N40" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2432,42 +2598,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="I41" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="J41" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="K41" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="L41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="M41" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="M41" s="12" t="n">
+      <c r="N41" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2486,42 +2657,47 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>VIA MILANO 108</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>CERRI SARA</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="I42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="J42" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="K42" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="M42" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="N42" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2540,42 +2716,47 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>GALVANI 34</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>ROMANO CARMELA</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="I43" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="J43" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="K43" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K43" s="12" t="n">
+      <c r="L43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="M43" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="M43" s="12" t="n">
+      <c r="N43" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2592,40 +2773,45 @@
           <t>CANTÙ</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>RONCO VIA VERGANI</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>RAVA CLAUDIO</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="I44" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="J44" s="12" t="n">
         <v>5</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="M44" s="12" t="n">
+      <c r="N44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2642,26 +2828,28 @@
           <t>VALMADRERA</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>VIA XXV APRILE 22</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="I45" s="12" t="n">
         <v>43</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>0</v>
@@ -2675,7 +2863,10 @@
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -2483,11 +2483,7 @@
           <t>VIA CERCA  FRAZ.CALEPPIO 21</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>CERRI SARA</t>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3874</v>
+        <v>4074</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2999</v>
+        <v>3153</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2560</v>
+        <v>2713</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>775</v>
+        <v>813</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,52 +901,52 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>02591</t>
+          <t>01805</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>VOGHERA</t>
+          <t>APPIANO GENTILE</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA CARLO EMANUELE 5</t>
+          <t>STRADA PROV.LE N.23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,35 +956,35 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>351</v>
+        <v>458</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>231</v>
+        <v>423</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>158</v>
+        <v>66</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>01805</t>
+          <t>02591</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>APPIANO GENTILE</t>
+          <t>VOGHERA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>STRADA PROV.LE N.23</t>
+          <t>VIA CARLO EMANUELE 5</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>443</v>
+        <v>367</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>396</v>
+        <v>249</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
+        <v>211</v>
+      </c>
+      <c r="G15" s="12" t="n">
         <v>196</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <v>182</v>
-      </c>
       <c r="H15" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA/LIGURIA</t>
+          <t>V.LE BRIANZA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,39 +1192,39 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>163</v>
+        <v>279</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L17" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="N17" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="M17" s="12" t="n">
-        <v>295</v>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>64</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>15</v>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>V.LE BRIANZA</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>263</v>
+        <v>217</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CORSO MATTEOTTI CASTELLO</t>
+          <t>VIALE EUROPA/LIGURIA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>183</v>
+        <v>308</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>12</v>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>27</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>91</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE ANG.GARIBALDI</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,39 +1841,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
+          <t>TRIESTE ANG.GARIBALDI</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,39 +1959,39 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>10</v>
@@ -2043,10 +2043,10 @@
         <v>20</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA DI VITTORIO, 14</t>
+          <t>SS 10 KM 154+108</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="H32" s="12" t="n">
+      <c r="K32" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L32" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I32" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="M32" s="12" t="n">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 154+108</t>
+          <t>VIA GALLARATE 40</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA GALLARATE 40</t>
+          <t>VIA DI VITTORIO, 14</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,35 +2195,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>9</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
@@ -2320,25 +2320,25 @@
         <v>43</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>30</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>21</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>9</v>
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>10</v>
@@ -2397,7 +2397,7 @@
         <v>6</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>8</v>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>17</v>
@@ -2453,10 +2453,10 @@
         <v>6</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>7</v>
@@ -2493,7 +2493,7 @@
         <v>31</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>26</v>
@@ -2525,17 +2525,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>SP 35 DEI GIOVI KM 132+300</t>
+          <t>VIA MILANO 108</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2545,39 +2545,39 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H40" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J40" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="K40" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2608,31 +2608,31 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2643,17 +2643,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA MILANO 108</t>
+          <t>SP 35 DEI GIOVI KM 132+300</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2663,35 +2663,35 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I42" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="N42" s="12" t="n">
         <v>5</v>
-      </c>
-      <c r="L42" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>24</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>2</v>
@@ -2784,13 +2784,13 @@
         <v>7</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>5</v>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4074</v>
+        <v>4264</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3153</v>
+        <v>3296</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2713</v>
+        <v>2848</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>397</v>
+        <v>416</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>541</v>
+        <v>565</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>813</v>
+        <v>852</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>423</v>
+        <v>448</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>143</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>117</v>
@@ -1040,7 +1040,7 @@
         <v>59</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>172</v>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I16" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>174</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J16" s="12" t="n">
-        <v>167</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="M16" s="12" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1255,52 +1255,52 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>366</v>
+        <v>207</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>CORSO MATTEOTTI CASTELLO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>217</v>
+        <v>298</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="K19" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="L19" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="L19" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="M19" s="12" t="n">
-        <v>192</v>
+        <v>388</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>65</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>20</v>
@@ -1444,16 +1444,16 @@
         <v>20</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>12</v>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>36</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>27</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,35 +1727,35 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>21</v>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
+          <t>TRIESTE ANG.GARIBALDI</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIALE PAPINIANO  54 54</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1904,52 +1904,52 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE ANG.GARIBALDI</t>
+          <t>VIALE PAPINIANO  54 54</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I30" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="L30" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="J30" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="M30" s="12" t="n">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SS.234 KM 9+250</t>
+          <t>SS 10 KM 154+108</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2022,52 +2022,52 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I31" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L31" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J31" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="M31" s="12" t="n">
-        <v>153</v>
+        <v>38</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 154+108</t>
+          <t>SS.234 KM 9+250</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2081,52 +2081,52 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>34</v>
+        <v>156</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA GALLARATE 40</t>
+          <t>VIA DI VITTORIO, 14</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L33" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M33" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="N33" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="M33" s="12" t="n">
-        <v>152</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>22</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA DI VITTORIO, 14</t>
+          <t>VIA GALLARATE 40</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,35 +2195,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
         <v>53</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>5</v>
+        <v>128</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>51</v>
@@ -2270,30 +2270,30 @@
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA MURAT 14</t>
+          <t>PL LOTTO 14/A ANG VI ELIA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2320,28 +2320,28 @@
         <v>43</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K36" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M36" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="N36" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>123</v>
-      </c>
-      <c r="N36" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>PL LOTTO 14/A ANG VI ELIA</t>
+          <t>VIA MURAT 14</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>7</v>
@@ -2470,20 +2470,24 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA CERCA  FRAZ.CALEPPIO 21</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>VIA MILANO 108</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>CERRI SARA</t>
@@ -2493,28 +2497,28 @@
         <v>31</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2525,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA MILANO 108</t>
+          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,94 +2553,90 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+          <t>VIA CERCA  FRAZ.CALEPPIO 21</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
           <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J41" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="K41" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2667,16 +2667,16 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>31</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>16</v>
@@ -2685,10 +2685,10 @@
         <v>2</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>5</v>
@@ -2726,19 +2726,19 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>42</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>6</v>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>2</v>
@@ -2784,13 +2784,13 @@
         <v>7</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>5</v>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4264</v>
+        <v>4474</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3296</v>
+        <v>3455</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2848</v>
+        <v>3052</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>565</v>
+        <v>600</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>852</v>
+        <v>907</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>366</v>
+        <v>408</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>485</v>
+        <v>518</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
+        <v>238</v>
+      </c>
+      <c r="G15" s="12" t="n">
         <v>223</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <v>204</v>
-      </c>
       <c r="H15" s="12" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>V.LE BRIANZA</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CORSO MATTEOTTI CASTELLO</t>
+          <t>V.LE BRIANZA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,56 +1251,56 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>230</v>
+        <v>321</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>207</v>
+        <v>284</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>VIALE EUROPA/LIGURIA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>298</v>
+        <v>197</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>18</v>
+        <v>156</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>388</v>
+        <v>335</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA/LIGURIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>175</v>
+        <v>320</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>318</v>
+        <v>413</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>51832</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>OSNAGO</t>
+          <t>LIMBIATE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SS 36 KM 30+083</t>
+          <t>VIALE DEI MILLE</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>56133</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>LIMBIATE</t>
+          <t>OSNAGO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEI MILLE</t>
+          <t>SS 36 KM 30+083</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,39 +1723,39 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1786,52 +1786,52 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>26</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>21</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02275</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SANT'ANGELO LODIGIANO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>TRIESTE ANG.GARIBALDI</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>02275</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>SANT'ANGELO LODIGIANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
+          <t>TRIESTE ANG.GARIBALDI</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>16</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>8</v>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>18</v>
@@ -2202,32 +2202,32 @@
         <v>53</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>99</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>39</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>23</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>24</v>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>10</v>
@@ -2279,14 +2279,14 @@
         <v>10</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2317,31 +2317,31 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>21</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>9</v>
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>7</v>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA MILANO 108</t>
+          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,16 +2494,16 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>27</v>
@@ -2512,34 +2512,34 @@
         <v>6</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
+          <t>VIA MILANO 108</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2553,35 +2553,35 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2611,13 @@
         <v>31</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>22</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2667,19 +2667,19 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>31</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>2</v>
@@ -2688,7 +2688,7 @@
         <v>14</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>5</v>
@@ -2741,13 +2741,13 @@
         <v>17</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>2</v>
@@ -2784,13 +2784,13 @@
         <v>7</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>5</v>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4474</v>
+        <v>4668</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3455</v>
+        <v>3602</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3052</v>
+        <v>3222</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>600</v>
+        <v>627</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>118</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>907</v>
+        <v>958</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>379</v>
+        <v>409</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>483</v>
+        <v>510</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="K17" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>234</v>
+      </c>
+      <c r="N17" s="12" t="n">
         <v>64</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>223</v>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>59</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>22</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         <v>158</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>121</v>
@@ -1512,14 +1512,14 @@
         <v>42</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>42</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>30</v>
@@ -1630,10 +1630,10 @@
         <v>33</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>44</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>59047</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>COMO</t>
+          <t>SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA CECILIO 1</t>
+          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>214</v>
+        <v>162</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>59047</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO MILANESE</t>
+          <t>COMO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIALE LOMBARDIA 2 ANGOLO VIA VOLTURNO</t>
+          <t>VIA CECILIO 1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>63</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>50</v>
@@ -1966,13 +1966,13 @@
         <v>74</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>59</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>59</v>
@@ -1984,14 +1984,14 @@
         <v>16</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>18</v>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA GALLARATE 40</t>
+          <t>VIA GARIBALDI 197</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>55673</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI 197</t>
+          <t>VIA GALLARATE 40</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,39 +2254,39 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>12</v>
@@ -2338,7 +2338,7 @@
         <v>7</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>12</v>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>2</v>
@@ -2394,10 +2394,10 @@
         <v>8</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>9</v>
@@ -2438,13 +2438,13 @@
         <v>40</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>30</v>
@@ -2456,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>7</v>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>52221</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>PAULLO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
+          <t>VIA MILANO 108</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,52 +2494,52 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="N39" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>93</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="N39" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>52221</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PAULLO</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA MILANO 108</t>
+          <t>PIAZZA TRENTO 38 ANGOLO VIALE ISONZO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2553,35 +2553,35 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K40" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L40" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="M40" s="12" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2611,13 @@
         <v>31</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>22</v>
@@ -2670,13 +2670,13 @@
         <v>30</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>31</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>17</v>
@@ -2688,7 +2688,7 @@
         <v>14</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>5</v>
@@ -2726,19 +2726,19 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>42</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>7</v>
@@ -2747,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2784,13 +2784,13 @@
         <v>7</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>5</v>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O45" headerRowCount="1">
-  <autoFilter ref="A10:O45"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O46" headerRowCount="1">
+  <autoFilter ref="A10:O46"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4668</v>
+        <v>4925</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3602</v>
+        <v>3800</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3222</v>
+        <v>3437</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>156</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>958</v>
+        <v>1018</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,35 +901,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>458</v>
+        <v>488</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>542</v>
+        <v>569</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="K15" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="L15" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="L15" s="12" t="n">
-        <v>70</v>
-      </c>
       <c r="M15" s="12" t="n">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CORSO MATTEOTTI CASTELLO</t>
+          <t>V.LE BRIANZA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>258</v>
+        <v>352</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>234</v>
+        <v>310</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>V.LE BRIANZA</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,56 +1251,56 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>342</v>
+        <v>272</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>48</v>
+        <v>143</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02316</t>
+          <t>02384</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>COLOGNO MONZESE</t>
+          <t>DESIO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIALE EUROPA/LIGURIA</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>217</v>
+        <v>359</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>162</v>
+        <v>30</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>353</v>
+        <v>455</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02384</t>
+          <t>02316</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>DESIO</t>
+          <t>COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>VIALE EUROPA/LIGURIA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>345</v>
+        <v>242</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>25</v>
+        <v>169</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>429</v>
+        <v>365</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>161</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>44</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>39</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>21</v>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>56232</t>
+          <t>01844</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>FINO MORNASCO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIALE PAPINIANO  54 54</t>
+          <t>VIA GARIBALDI 197</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L30" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J30" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="M30" s="12" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>02556</t>
+          <t>56232</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>BRONI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SS 10 KM 154+108</t>
+          <t>VIALE PAPINIANO  54 54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="G31" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G31" s="12" t="n">
-        <v>112</v>
-      </c>
       <c r="H31" s="12" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>9</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>02164</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CASALPUSTERLENGO</t>
+          <t>PESCHIERA BORROMEO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SS.234 KM 9+250</t>
+          <t>VIA DI VITTORIO, 14</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,35 +2077,35 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>02556</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA BORROMEO</t>
+          <t>BRONI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA DI VITTORIO, 14</t>
+          <t>SS 10 KM 154+108</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="H33" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I33" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I33" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="J33" s="12" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>166</v>
+        <v>59</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>01844</t>
+          <t>02164</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>FINO MORNASCO</t>
+          <t>CASALPUSTERLENGO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA GARIBALDI 197</t>
+          <t>SS.234 KM 9+250</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,39 +2195,39 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2258,19 +2258,19 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>16</v>
@@ -2279,10 +2279,10 @@
         <v>18</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>12</v>
@@ -2338,10 +2338,10 @@
         <v>7</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>9</v>
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>7</v>
@@ -2494,31 +2494,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2553,19 +2553,19 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>8</v>
@@ -2574,7 +2574,7 @@
         <v>7</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>19</v>
@@ -2611,13 +2611,13 @@
         <v>31</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>22</v>
@@ -2667,28 +2667,28 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>31</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>5</v>
@@ -2726,19 +2726,19 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>42</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>7</v>
@@ -2747,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2784,13 +2784,13 @@
         <v>7</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>5</v>
@@ -2865,6 +2865,61 @@
       <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>12413</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SEGRATE</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>S.P.RIVOLTANA N. 14</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>ROMANO CARMELA</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4925</v>
+        <v>5178</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3800</v>
+        <v>3980</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3437</v>
+        <v>3684</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>647</v>
+        <v>689</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>503</v>
+        <v>527</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>1018</v>
+        <v>1074</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>415</v>
+        <v>448</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>455</v>
+        <v>483</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>55</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>V.LE BRIANZA</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>352</v>
+        <v>286</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>77</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CORSO MATTEOTTI CASTELLO</t>
+          <t>V.LE BRIANZA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,39 +1251,39 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>272</v>
+        <v>364</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>143</v>
+        <v>67</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>248</v>
+        <v>333</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>53</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>18</v>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>46</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>40</v>
@@ -1512,10 +1512,10 @@
         <v>44</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1730,13 +1730,13 @@
         <v>124</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>90</v>
@@ -1748,10 +1748,10 @@
         <v>42</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>39</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>21</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="H29" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="I29" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>64</v>
-      </c>
       <c r="K29" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L29" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L29" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="M29" s="12" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>52</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,35 +2022,35 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>16</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>29</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>8</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>9</v>
@@ -2199,19 +2199,19 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>11</v>
@@ -2220,10 +2220,10 @@
         <v>23</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,31 +2258,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,31 +2317,31 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>9</v>
@@ -2397,7 +2397,7 @@
         <v>22</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>9</v>
@@ -2435,19 +2435,19 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>18</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>7</v>
@@ -2456,10 +2456,10 @@
         <v>15</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2494,19 +2494,19 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>10</v>
@@ -2515,10 +2515,10 @@
         <v>6</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2556,13 +2556,13 @@
         <v>39</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>34</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>33</v>
@@ -2574,10 +2574,10 @@
         <v>7</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2588,51 +2588,55 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02414</t>
+          <t>12416</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>SETTALA</t>
+          <t>PADERNO DUGNANO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA CERCA  FRAZ.CALEPPIO 21</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>SP 35 DEI GIOVI KM 132+300</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="H41" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="I41" s="12" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2643,55 +2647,51 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>02414</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>PADERNO DUGNANO</t>
+          <t>SETTALA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>SP 35 DEI GIOVI KM 132+300</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Nadir Abdel</t>
-        </is>
-      </c>
+          <t>VIA CERCA  FRAZ.CALEPPIO 21</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
         <v>31</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2747,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2784,13 +2784,13 @@
         <v>7</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>5</v>
@@ -2816,39 +2816,39 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>57111</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>VALMADRERA</t>
+          <t>SEGRATE</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA XXV APRILE 22</t>
+          <t>S.P.RIVOLTANA N. 14</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="H45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J45" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>0</v>
@@ -2857,50 +2857,50 @@
         <v>0</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>57111</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SEGRATE</t>
+          <t>VALMADRERA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>S.P.RIVOLTANA N. 14</t>
+          <t>VIA XXV APRILE 22</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>0</v>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5178</v>
+        <v>5397</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3980</v>
+        <v>4176</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3684</v>
+        <v>3961</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>689</v>
+        <v>709</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>527</v>
+        <v>560</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>1074</v>
+        <v>1140</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>448</v>
+        <v>474</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>483</v>
+        <v>506</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>585</v>
+        <v>607</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>55</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>554</v>
+        <v>590</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>66</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01837</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LECCO</t>
+          <t>MARIANO COMENSE</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>CORSO MATTEOTTI CASTELLO</t>
+          <t>V.LE BRIANZA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>286</v>
+        <v>374</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>279</v>
+        <v>351</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>56030</t>
+          <t>01837</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MARIANO COMENSE</t>
+          <t>LECCO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>V.LE BRIANZA</t>
+          <t>CORSO MATTEOTTI CASTELLO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,39 +1251,39 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>RAVA CLAUDIO</t>
+          <t>ADINOLFI VINCENZO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>482</v>
+        <v>517</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>17</v>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>51668</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>LODI</t>
+          <t>MILANO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VL EUROPA</t>
+          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>DELLERBA ALBERTO</t>
+          <t>CERRI SARA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>416</v>
+        <v>346</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>51668</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MILANO</t>
+          <t>LODI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA ANTONINI ANGOLO VERRO SNC</t>
+          <t>VL EUROPA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CERRI SARA</t>
+          <t>DELLERBA ALBERTO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>326</v>
+        <v>450</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>39</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>24</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>52</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>37</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>66</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>23</v>
@@ -2043,10 +2043,10 @@
         <v>16</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>102</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>6</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>8</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>9</v>
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2258,16 +2258,16 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>43</v>
@@ -2276,13 +2276,13 @@
         <v>16</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,19 +2317,19 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>14</v>
@@ -2338,10 +2338,10 @@
         <v>8</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>9</v>
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2494,31 +2494,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>35</v>
-      </c>
       <c r="K39" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2553,31 +2553,31 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="H41" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>31</v>
-      </c>
       <c r="I41" s="12" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2670,13 +2670,13 @@
         <v>31</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>26</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>22</v>
@@ -2747,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2784,13 +2784,13 @@
         <v>7</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>47</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>5</v>
@@ -2857,14 +2857,14 @@
         <v>0</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O46" headerRowCount="1">
-  <autoFilter ref="A10:O46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O47" headerRowCount="1">
+  <autoFilter ref="A10:O47"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5397</v>
+        <v>5405</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4176</v>
+        <v>4186</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3961</v>
+        <v>3962</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -2761,17 +2761,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>01923</t>
+          <t>01858</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CANTÙ</t>
+          <t>BREGNANO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>RONCO VIA VERGANI</t>
+          <t>S.P. 31  DELLA PIODA - VIA MILANO  79</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -2781,28 +2781,28 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>155</v>
+        <v>28</v>
       </c>
       <c r="J44" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K44" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L44" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>0</v>
@@ -2816,94 +2816,94 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>01923</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SEGRATE</t>
+          <t>CANTÙ</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>S.P.RIVOLTANA N. 14</t>
+          <t>RONCO VIA VERGANI</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ROMANO CARMELA</t>
+          <t>RAVA CLAUDIO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="12" t="n">
+      <c r="L45" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" s="12" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>57111</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>VALMADRERA</t>
+          <t>SEGRATE</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA XXV APRILE 22</t>
+          <t>S.P.RIVOLTANA N. 14</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>ADINOLFI VINCENZO</t>
+          <t>ROMANO CARMELA</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="12" t="n">
-        <v>26</v>
-      </c>
       <c r="H46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J46" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>0</v>
@@ -2912,12 +2912,67 @@
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>57111</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>VALMADRERA</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>VIA XXV APRILE 22</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>ADINOLFI VINCENZO</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - FALANGA ANIELLO.xlsx
@@ -684,13 +684,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5405</v>
+        <v>5497</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4186</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>3962</v>
+        <v>3899</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>709</v>
+        <v>692</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>560</v>
+        <v>533</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>229</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>359</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>146</v>
@@ -863,10 +863,10 @@
         <v>168</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>1140</v>
+        <v>1117</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,19 +901,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>199</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>408</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>214</v>
@@ -922,10 +922,10 @@
         <v>65</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>168</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>353</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>143</v>
@@ -981,7 +981,7 @@
         <v>55</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>108</v>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>216</v>
@@ -1031,7 +1031,7 @@
         <v>147</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>291</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>144</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>108</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>97</v>
@@ -1099,7 +1099,7 @@
         <v>86</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>87</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>114</v>
@@ -1149,7 +1149,7 @@
         <v>82</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>88</v>
@@ -1158,14 +1158,14 @@
         <v>52</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>127</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>40</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>51</v>
@@ -1217,7 +1217,7 @@
         <v>83</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>83</v>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>294</v>
@@ -1267,7 +1267,7 @@
         <v>56</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>75</v>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>45</v>
@@ -1326,7 +1326,7 @@
         <v>125</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>55</v>
@@ -1335,10 +1335,10 @@
         <v>65</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,19 +1373,19 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>67</v>
@@ -1394,14 +1394,14 @@
         <v>87</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>66</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>60</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>92</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>42</v>
@@ -1512,7 +1512,7 @@
         <v>45</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>143</v>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>35</v>
@@ -1571,10 +1571,10 @@
         <v>43</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>194</v>
@@ -1621,7 +1621,7 @@
         <v>86</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>46</v>
@@ -1630,14 +1630,14 @@
         <v>47</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>168</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>174</v>
@@ -1680,7 +1680,7 @@
         <v>115</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>73</v>
@@ -1689,10 +1689,10 @@
         <v>13</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>223</v>
@@ -1739,7 +1739,7 @@
         <v>56</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>45</v>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>39</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>17</v>
@@ -1807,7 +1807,7 @@
         <v>42</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>110</v>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>102</v>
@@ -1857,7 +1857,7 @@
         <v>37</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>29</v>
@@ -1866,14 +1866,14 @@
         <v>25</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>24</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>24</v>
@@ -1925,7 +1925,7 @@
         <v>24</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>59</v>
@@ -1966,7 +1966,7 @@
         <v>92</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>61</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>18</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>66</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>23</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>22</v>
@@ -2093,7 +2093,7 @@
         <v>6</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>21</v>
@@ -2143,16 +2143,16 @@
         <v>78</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>35</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>43</v>
@@ -2211,7 +2211,7 @@
         <v>25</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>12</v>
@@ -2220,14 +2220,14 @@
         <v>23</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>49</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>94</v>
@@ -2267,10 +2267,10 @@
         <v>118</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>16</v>
@@ -2293,7 +2293,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>56055</t>
+          <t>02222</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>PL LOTTO 14/A ANG VI ELIA</t>
+          <t>VIA MURAT 14</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2317,31 +2317,31 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>47</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>203</v>
+        <v>154</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02222</t>
+          <t>56055</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA MURAT 14</t>
+          <t>PL LOTTO 14/A ANG VI ELIA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2376,31 +2376,31 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>47</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2438,16 +2438,16 @@
         <v>49</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>8</v>
@@ -2456,7 +2456,7 @@
         <v>15</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>11</v>
@@ -2506,7 +2506,7 @@
         <v>4</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>12</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2553,19 +2553,19 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>98</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>122</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>9</v>
@@ -2574,7 +2574,7 @@
         <v>7</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>26</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>120</v>
@@ -2624,7 +2624,7 @@
         <v>98</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>4</v>
@@ -2676,10 +2676,10 @@
         <v>26</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>7</v>
@@ -2688,7 +2688,7 @@
         <v>9</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>4</v>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>42</v>
@@ -2738,7 +2738,7 @@
         <v>5</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>7</v>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>103</v>
@@ -2793,7 +2793,7 @@
         <v>28</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>5</v>
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>1</v>
@@ -2857,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>0</v>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2949,13 +2949,13 @@
         <v>0</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J47" s="12" t="n">
         <v>0</v>
